--- a/FitCheck_os/fitcheck_cleaned_export.xlsx
+++ b/FitCheck_os/fitcheck_cleaned_export.xlsx
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -80,6 +80,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2262,31 +2264,31 @@
           <t>PID_003__2026-03-13__C04__T01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>24.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -2409,31 +2411,31 @@
           <t>PID_003__2026-03-13__C01__T01</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -2560,31 +2562,31 @@
           <t>PID_003__2026-03-13__C02__T01</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>51.3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>25.6</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -2707,31 +2709,31 @@
           <t>PID_003__2026-03-13__C03__T01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>51.3</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -2854,31 +2856,31 @@
           <t>PID_004__2026-03-14__C11__T01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>48.26</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -2997,31 +2999,31 @@
           <t>PID_004__2026-03-14__C01__T01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -3144,31 +3146,31 @@
           <t>PID_004__2026-03-14__C02__T01</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>55.6</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -3291,31 +3293,31 @@
           <t>PID_004__2026-03-14__C03__T01</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>53.2</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="5" t="n">
         <v>20.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -3438,31 +3440,31 @@
           <t>PID_004__2026-03-14__C04__T01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>58.6</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -3581,31 +3583,31 @@
           <t>PID_004__2026-03-18__C05__T01</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="5" t="n">
         <v>25.7</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -3728,31 +3730,31 @@
           <t xml:space="preserve"> PID_004__2026-03-18__C06__T01</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>57.8</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -3875,31 +3877,31 @@
           <t>PID_004__2026-03-18__C07__T01</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>56.9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -4022,31 +4024,31 @@
           <t>PID_004__2026-03-18__C08__T01</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>55.9</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -4169,31 +4171,31 @@
           <t>PID_004__2026-03-18__C09__T01</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>55.8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -4312,31 +4314,31 @@
           <t>PID_004__2026-03-18__C10__T01</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -4459,31 +4461,31 @@
           <t>PID_003__2026-03-20__C05__T01</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -4602,31 +4604,31 @@
           <t>PID_003__2026-03-20__C06__T01</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -4749,31 +4751,31 @@
           <t>PID_003__2026-03-20__C07__T01</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>44.5</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -4896,31 +4898,31 @@
           <t>PID_003__2026-03-20__C08__T01</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -5043,31 +5045,31 @@
           <t>PID_003__2026-03-20__C09__T01</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="5" t="n">
         <v>19.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -5186,31 +5188,31 @@
           <t>PID_003__2026-03-20__C10__T01</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>39.8</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -5333,31 +5335,31 @@
           <t>PID_003__2026-03-20__C11__T01</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -5476,31 +5478,31 @@
           <t>PID_005__2026-04-17__C10__T01</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>49.4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="5" t="n">
         <v>21.3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -5669,31 +5671,31 @@
           <t>PID_005__2026-04-17__C05__T01</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="5" t="n">
         <v>43.5</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>50.2</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -5866,31 +5868,31 @@
           <t>PID_005__2026-04-17__C08__T01</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -6067,31 +6069,31 @@
           <t>PID_005__2026-04-17__C01__T01</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="6" t="n">
         <v>36186</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>59.6</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -6260,31 +6262,31 @@
           <t>PID_005__2026-04-17__C02__T01</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
         <v>56.5</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -6457,31 +6459,31 @@
           <t>PID_005__2026-04-17__C11__T01</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>53.5</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -6662,31 +6664,31 @@
           <t>PID_005__2026-04-17__C09__T01</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
         <v>49.8</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -6851,31 +6853,31 @@
           <t>PID_005__2026-04-17__C04__T01</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -7040,31 +7042,31 @@
           <t>PID_005__2026-04-17__C07__T01</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
         <v>54.7</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -7245,31 +7247,31 @@
           <t>PID_005__2026-04-17__C04__T01</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>50.6</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -7446,31 +7448,31 @@
           <t>PID_005__2026-04-17__C03__T01</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>51.6</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -7639,31 +7641,31 @@
           <t>PID_006__2026-04-18__C08__T01</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -7836,31 +7838,31 @@
           <t>PID_006__2026-04-18__C05__T01</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="5" t="n">
         <v>43.8</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="5" t="n">
         <v>28.2</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -8025,31 +8027,31 @@
           <t>PID_006__2026-04-18__C02__T01</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>58.6</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -8222,31 +8224,31 @@
           <t>PID_006__2026-04-18__C10__T01</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
         <v>54.4</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="5" t="n">
         <v>28.8</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -8415,31 +8417,31 @@
           <t>PID_006__2026-04-18__C01__T01</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>57.8</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -8604,31 +8606,31 @@
           <t>PID_006__2026-04-18__C11__T01</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="F40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
         <v>52.9</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -8797,31 +8799,31 @@
           <t>PID_006__2026-04-18__C07__T01</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -8986,31 +8988,31 @@
           <t>PID_006__2026-04-18__C04__T01</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
         <v>56.9</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -9175,31 +9177,31 @@
           <t>PID_006__2026-04-18__C06__T01</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>51.4</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="5" t="n">
         <v>26.4</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -9364,31 +9366,31 @@
           <t>PID_006__2026-04-18__C09__T01</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="5" t="n">
         <v>27.6</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -9549,31 +9551,31 @@
           <t>PID_006__2026-04-18__C03__T01</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>55.5</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="5" t="n">
         <v>22.6</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -9742,31 +9744,31 @@
           <t>PID_007__2026-04-25__C11__T01</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="5" t="n">
         <v>26.2</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -9937,31 +9939,31 @@
           <t>PID_007__2026-04-28__C01__T01</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -10134,31 +10136,31 @@
           <t>PID_007__2026-04-25__C05__T01</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="5" t="n">
         <v>43.8</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="F48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
         <v>40.7</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="5" t="n">
         <v>26.8</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -10335,31 +10337,31 @@
           <t>PID_007__2026-04-25__C08__T01</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
         <v>44.9</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="5" t="n">
         <v>25.7</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -10532,31 +10534,31 @@
           <t>PID_007__2026-04-25__C09__T01</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="F50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -10725,31 +10727,31 @@
           <t>PID_007__2026-04-25__C10__T01</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -10922,31 +10924,31 @@
           <t>PID_007__2026-04-25__C06__T01</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="F52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
         <v>45.5</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
@@ -11119,31 +11121,31 @@
           <t>PID_007__2026-04-25__C04__T01</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="5" t="n">
         <v>26.9</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K53" t="inlineStr">
@@ -11312,31 +11314,31 @@
           <t>PID_007__2026-04-25__C02__T01</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="K54" t="inlineStr">
@@ -11517,31 +11519,31 @@
           <t>PID_007__2026-04-25__C03__T01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
@@ -11714,31 +11716,31 @@
           <t>PID_007__2026-04-25__C07__T01</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
@@ -12765,52 +12767,52 @@
           <t>JO_EN</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="5" t="n">
         <v>46.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="5" t="n">
         <v>34.2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="5" t="n">
         <v>40.2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>26.6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="5" t="n">
         <v>44.9</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="5" t="n">
         <v>59.8</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="5" t="n">
         <v>45.6</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="5" t="n">
         <v>21.1</v>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -12829,52 +12831,52 @@
           <t>EN_JO</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="5" t="n">
         <v>34.2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="5" t="n">
         <v>45.4</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="5" t="n">
         <v>41.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="5" t="n">
         <v>30.2</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="5" t="n">
         <v>57.4</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="5" t="n">
         <v>53.5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="5" t="n">
         <v>24.7</v>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -12893,52 +12895,52 @@
           <t>JO_EN</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="5" t="n">
         <v>56.8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="5" t="n">
         <v>34.3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="5" t="n">
         <v>44.2</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>24.3</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="5" t="n">
         <v>27.1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="5" t="n">
         <v>60.3</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="5" t="n">
         <v>84.5</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="5" t="n">
         <v>61.2</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="5" t="n">
         <v>34.4</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="5" t="n">
         <v>80.3</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="5" t="n">
         <v>61.8</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="5" t="n">
         <v>52.4</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="5" t="n">
         <v>24.8</v>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -12957,52 +12959,52 @@
           <t>EN_JO</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>48.4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="5" t="n">
         <v>41.4</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="5" t="n">
         <v>23.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="5" t="n">
         <v>23.1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="5" t="n">
         <v>68.3</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="5" t="n">
         <v>49.6</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>52.9</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="5" t="n">
         <v>29.4</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="5" t="n">
         <v>37.9</v>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -13021,50 +13023,50 @@
           <t>EN_JO</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>45.8</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="5" t="n">
         <v>27.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="5" t="n">
         <v>137.16</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="5" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="5" t="n">
         <v>56.9</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="5" t="n">
         <v>28.9</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="5" t="n">
         <v>26.6</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="n">
         <v>42.7</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="5" t="n">
         <v>23.4</v>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -14070,31 +14072,31 @@
           <t>PID_003__2026-03-13__C04__T01</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>24.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -14201,31 +14203,31 @@
           <t>PID_003__2026-03-13__C01__T01</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
         <v>50.3</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -14332,31 +14334,31 @@
           <t>PID_003__2026-03-13__C02__T01</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>51.3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>25.6</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -14459,31 +14461,31 @@
           <t>PID_003__2026-03-13__C03__T01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>51.3</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -14586,31 +14588,31 @@
           <t>PID_004__2026-03-14__C11__T01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>48.26</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -14713,31 +14715,31 @@
           <t>PID_004__2026-03-14__C01__T01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -14840,31 +14842,31 @@
           <t>PID_004__2026-03-14__C02__T01</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>55.6</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -14967,31 +14969,31 @@
           <t>PID_004__2026-03-14__C03__T01</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>53.2</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="5" t="n">
         <v>20.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -15094,31 +15096,31 @@
           <t>PID_004__2026-03-14__C04__T01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>58.6</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -15221,31 +15223,31 @@
           <t>PID_004__2026-03-18__C05__T01</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="5" t="n">
         <v>25.7</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -15352,31 +15354,31 @@
           <t xml:space="preserve"> PID_004__2026-03-18__C06__T01</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>57.8</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -15479,31 +15481,31 @@
           <t>PID_004__2026-03-18__C07__T01</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>56.9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -15606,31 +15608,31 @@
           <t>PID_004__2026-03-18__C08__T01</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>55.9</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -15733,31 +15735,31 @@
           <t>PID_004__2026-03-18__C09__T01</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>55.8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -15860,31 +15862,31 @@
           <t>PID_004__2026-03-18__C10__T01</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -15987,31 +15989,31 @@
           <t>PID_003__2026-03-20__C05__T01</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -16114,31 +16116,31 @@
           <t>PID_003__2026-03-20__C06__T01</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -16241,31 +16243,31 @@
           <t>PID_003__2026-03-20__C07__T01</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>44.5</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -16368,31 +16370,31 @@
           <t>PID_003__2026-03-20__C08__T01</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -16495,31 +16497,31 @@
           <t>PID_003__2026-03-20__C09__T01</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="5" t="n">
         <v>19.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -16622,31 +16624,31 @@
           <t>PID_003__2026-03-20__C10__T01</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
         <v>39.8</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -16749,31 +16751,31 @@
           <t>PID_003__2026-03-20__C11__T01</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="5" t="n">
         <v>3</v>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -16876,31 +16878,31 @@
           <t>PID_005__2026-04-17__C10__T01</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>49.4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="5" t="n">
         <v>21.3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -17049,31 +17051,31 @@
           <t>PID_005__2026-04-17__C05__T01</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="5" t="n">
         <v>43.5</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>50.2</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -17230,31 +17232,31 @@
           <t>PID_005__2026-04-17__C08__T01</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>55.2</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -17411,31 +17413,31 @@
           <t>PID_005__2026-04-17__C01__T01</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="6" t="n">
         <v>36186</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>59.6</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -17584,31 +17586,31 @@
           <t>PID_005__2026-04-17__C02__T01</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
         <v>56.5</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -17761,31 +17763,31 @@
           <t>PID_005__2026-04-17__C11__T01</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>53.5</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -17950,31 +17952,31 @@
           <t>PID_005__2026-04-17__C09__T01</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
         <v>49.8</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -18123,31 +18125,31 @@
           <t>PID_005__2026-04-17__C04__T01</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -18296,31 +18298,31 @@
           <t>PID_005__2026-04-17__C07__T01</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
         <v>54.7</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -18481,31 +18483,31 @@
           <t>PID_005__2026-04-17__C04__T01</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>50.6</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -18666,31 +18668,31 @@
           <t>PID_005__2026-04-17__C03__T01</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
         <v>51.6</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -18839,31 +18841,31 @@
           <t>PID_006__2026-04-18__C08__T01</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -19016,31 +19018,31 @@
           <t>PID_006__2026-04-18__C05__T01</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="5" t="n">
         <v>43.8</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="5" t="n">
         <v>28.2</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -19189,31 +19191,31 @@
           <t>PID_006__2026-04-18__C02__T01</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>58.6</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -19366,31 +19368,31 @@
           <t>PID_006__2026-04-18__C10__T01</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
         <v>54.4</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="5" t="n">
         <v>28.8</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -19539,31 +19541,31 @@
           <t>PID_006__2026-04-18__C01__T01</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>57.8</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -19708,31 +19710,31 @@
           <t>PID_006__2026-04-18__C11__T01</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="F40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
         <v>52.9</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -19885,31 +19887,31 @@
           <t>PID_006__2026-04-18__C07__T01</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -20054,31 +20056,31 @@
           <t>PID_006__2026-04-18__C04__T01</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
         <v>56.9</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -20227,31 +20229,31 @@
           <t>PID_006__2026-04-18__C06__T01</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>51.4</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="5" t="n">
         <v>26.4</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -20396,31 +20398,31 @@
           <t>PID_006__2026-04-18__C09__T01</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="5" t="n">
         <v>27.6</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -20565,31 +20567,31 @@
           <t>PID_006__2026-04-18__C03__T01</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>55.5</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="5" t="n">
         <v>22.6</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -20738,31 +20740,31 @@
           <t>PID_007__2026-04-25__C11__T01</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="5" t="n">
         <v>26.2</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -20917,31 +20919,31 @@
           <t>PID_007__2026-04-28__C01__T01</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -21094,31 +21096,31 @@
           <t>PID_007__2026-04-25__C05__T01</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="5" t="n">
         <v>43.8</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="F48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
         <v>40.7</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="5" t="n">
         <v>26.8</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -21279,31 +21281,31 @@
           <t>PID_007__2026-04-25__C08__T01</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
         <v>44.9</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="5" t="n">
         <v>25.7</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -21456,31 +21458,31 @@
           <t>PID_007__2026-04-25__C09__T01</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="F50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -21633,31 +21635,31 @@
           <t>PID_007__2026-04-25__C10__T01</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -21810,31 +21812,31 @@
           <t>PID_007__2026-04-25__C06__T01</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="F52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
         <v>45.5</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
@@ -21987,31 +21989,31 @@
           <t>PID_007__2026-04-25__C04__T01</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="5" t="n">
         <v>26.9</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K53" t="inlineStr">
@@ -22164,31 +22166,31 @@
           <t>PID_007__2026-04-25__C02__T01</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="K54" t="inlineStr">
@@ -22349,31 +22351,31 @@
           <t>PID_007__2026-04-25__C03__T01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
@@ -22526,31 +22528,31 @@
           <t>PID_007__2026-04-25__C07__T01</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
@@ -23216,40 +23218,40 @@
           <t>Aeron Size A</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="5" t="n">
         <v>36.6</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="5" t="n">
         <v>41.7</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="5" t="n">
         <v>41.7</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="N2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>120</v>
       </c>
       <c r="R2" t="inlineStr">
@@ -23289,40 +23291,40 @@
           <t>Aeron Size B</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="5" t="n">
         <v>57.9</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="N3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="6" t="n">
         <v>120</v>
       </c>
       <c r="R3" t="inlineStr">
@@ -23362,40 +23364,40 @@
           <t>Aeron Size C</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="5" t="n">
         <v>40.1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="5" t="n">
         <v>57.9</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="N4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="6" t="n">
         <v>120</v>
       </c>
       <c r="R4" t="inlineStr">
@@ -23431,40 +23433,40 @@
           <t>Mirra 2</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="5" t="n">
         <v>52.1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="5" t="n">
         <v>41.3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="N5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="6" t="n">
         <v>115</v>
       </c>
       <c r="R5" t="inlineStr">
@@ -23500,40 +23502,40 @@
           <t>Generation</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="5" t="n">
         <v>43.8</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="5" t="n">
         <v>57.2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="5" t="n">
         <v>47.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="N6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>115</v>
       </c>
       <c r="R6" t="inlineStr">
@@ -23573,40 +23575,40 @@
           <t>Cosm Low Back</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="5" t="n">
         <v>57.2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="5" t="n">
         <v>39.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="6" t="n">
         <v>110</v>
       </c>
       <c r="R7" t="inlineStr">
@@ -23646,40 +23648,40 @@
           <t>Cosm Mid Back</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="5" t="n">
         <v>53.3</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="5" t="n">
         <v>39.4</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="5" t="n">
         <v>39.4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="N8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="6" t="n">
         <v>110</v>
       </c>
       <c r="R8" t="inlineStr">
@@ -23719,40 +23721,40 @@
           <t>Cosm High Back</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="5" t="n">
         <v>37.8</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="5" t="n">
         <v>53.3</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="5" t="n">
         <v>39.4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="5" t="n">
         <v>39.4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="N9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="6" t="n">
         <v>110</v>
       </c>
       <c r="R9" t="inlineStr">
@@ -23788,40 +23790,40 @@
           <t>Sayl</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="5" t="n">
         <v>52.1</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="N10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="6" t="n">
         <v>115</v>
       </c>
       <c r="R10" t="inlineStr">
@@ -23861,40 +23863,40 @@
           <t>Embody Gaming</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="5" t="n">
         <v>52.1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="5" t="n">
         <v>38.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="5" t="n">
         <v>38.1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="N11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="6" t="n">
         <v>120</v>
       </c>
       <c r="R11" t="inlineStr">
@@ -23930,40 +23932,40 @@
           <t>Vantum</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="5" t="n">
         <v>45.7</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="5" t="n">
         <v>55.9</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="5" t="n">
         <v>44.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="5" t="n">
         <v>44.5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="N12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="6" t="n">
         <v>110</v>
       </c>
       <c r="R12" t="inlineStr">
